--- a/data/subcontractors.xlsx
+++ b/data/subcontractors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbolanos\Desktop\projects\cps-tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2207B082-D7B8-4B01-BC07-C21C223F4ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0760F2-7880-474E-8CF7-8591E2A6CBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7FC67F31-20FD-4FEB-ADE5-67E343098000}"/>
+    <workbookView xWindow="28770" yWindow="1905" windowWidth="12105" windowHeight="11235" activeTab="1" xr2:uid="{7FC67F31-20FD-4FEB-ADE5-67E343098000}"/>
   </bookViews>
   <sheets>
     <sheet name="Subcontractors" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="46">
   <si>
     <t>name</t>
   </si>
@@ -166,6 +166,18 @@
   </si>
   <si>
     <t>Transport expenses to/from conversion site</t>
+  </si>
+  <si>
+    <t>M.S.E</t>
+  </si>
+  <si>
+    <t>Rue Léopold Demesmaeker 63</t>
+  </si>
+  <si>
+    <t>1083 Bruxelles</t>
+  </si>
+  <si>
+    <t>Placing CPS stickers &amp; seals</t>
   </si>
 </sst>
 </file>
@@ -631,7 +643,13 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
       </c>
       <c r="E5">
         <v>70</v>
@@ -722,7 +740,7 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -742,7 +760,7 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D5">
         <v>1</v>

--- a/data/subcontractors.xlsx
+++ b/data/subcontractors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbolanos\Desktop\projects\cps-tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0760F2-7880-474E-8CF7-8591E2A6CBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFAA458-8790-4F58-B05B-7199FDA56784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28770" yWindow="1905" windowWidth="12105" windowHeight="11235" activeTab="1" xr2:uid="{7FC67F31-20FD-4FEB-ADE5-67E343098000}"/>
+    <workbookView xWindow="7050" yWindow="1890" windowWidth="19485" windowHeight="11235" xr2:uid="{7FC67F31-20FD-4FEB-ADE5-67E343098000}"/>
   </bookViews>
   <sheets>
     <sheet name="Subcontractors" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="47">
   <si>
     <t>name</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>Placing CPS stickers &amp; seals</t>
+  </si>
+  <si>
+    <t>name_long</t>
   </si>
 </sst>
 </file>
@@ -561,97 +564,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C905FF-0BCF-4445-96D3-1B04879B7FE8}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>34</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>35</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>63.75</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
         <v>42</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>44</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>70</v>
       </c>
     </row>
